--- a/research/DUOL/Reports/DUOL_DCF_Model.xlsx
+++ b/research/DUOL/Reports/DUOL_DCF_Model.xlsx
@@ -1308,9 +1308,10 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31">
-        <f> NOPAT (after cash tax)</f>
-        <v>0</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>= NOPAT (after cash tax)</t>
+        </is>
       </c>
       <c r="C31" s="5">
         <f>C30*(1-C23)</f>
@@ -1945,9 +1946,10 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="8">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B8" s="5">
         <f>SUM(B5:B7)</f>
